--- a/examples/batch_report.xlsx
+++ b/examples/batch_report.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,17 +482,19 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>总步数</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
+          <t>批次号</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>B20260612-TEST01</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>已执行</t>
+          <t>总步数</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -502,52 +504,72 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>已执行</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>告警（有错误但继续）</t>
+          <t>跳过(resume)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>失败</t>
+          <t>成功</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>总耗时(秒)</t>
+          <t>告警（有错误但继续）</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.762</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>失败</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>总耗时(秒)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1.037</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>生成时间</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-06-12 01:40:46</t>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-12 02:00:41</t>
         </is>
       </c>
     </row>
@@ -635,9 +657,13 @@
         <v>1</v>
       </c>
       <c r="F2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
+        <v>0.37</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_上海.xlsx</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>命令返回退出码 1</t>
@@ -672,9 +698,13 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
+        <v>0.068</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_北京.xlsx</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>命令返回退出码 0</t>
@@ -709,9 +739,13 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.029</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>0.035</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_深圳.xlsx</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>命令返回退出码 0</t>
@@ -746,7 +780,7 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.079</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -783,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.099</v>
+        <v>0.113</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -820,7 +854,7 @@
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -857,7 +891,7 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.193</v>
+        <v>0.287</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -882,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -904,74 +938,119 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>合并三家花名册</t>
+          <t>校验上海分公司</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_上海.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>与Q1对比</t>
+          <t>校验北京分公司</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\Q1_Q2对比结果.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_北京.xlsx</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>生成脱敏版本</t>
+          <t>校验深圳分公司</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2_脱敏.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\校验结果_深圳.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>输出集团统计报告</t>
+          <t>合并三家花名册</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>E:\trae-bz\TraeProjects\1294\examples\上海总部_Q2明细.xlsx</t>
+          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>与Q1对比</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\Q1_Q2对比结果.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>生成脱敏版本</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\集团花名册_Q2_脱敏.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>输出集团统计报告</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>E:\trae-bz\TraeProjects\1294\examples\上海总部_Q2明细.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>输出集团统计报告</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>E:\trae-bz\TraeProjects\1294\examples\集团统计_Q2.xlsx</t>
         </is>
